--- a/ttl_long/AdHoc_Net_8.xlsx
+++ b/ttl_long/AdHoc_Net_8.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>105</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>97</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>271</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>168</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>178</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>337</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>141</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>224</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>332</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>263</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>505</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>372</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>337</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>473</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>555</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>232</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>651</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>302</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>638</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>785</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>251</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>769</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>286</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>745</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>959</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>168</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>990</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>285</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>951</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>951</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>1072</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>1063</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>303</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>257</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1230</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>1203</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1445</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>249</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1297</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>294</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1380</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1529</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>116</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1533</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>567</t>
         </is>
       </c>
     </row>
@@ -1004,199 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1273</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1242</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1383</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1540</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1545</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1462</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1554</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1540</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D134"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1244,7 +1057,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1266,7 +1079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1288,7 +1101,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1310,7 +1123,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1332,7 +1145,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1354,7 +1167,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1393,12 +1206,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1420,7 +1233,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1442,7 +1255,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1464,7 +1277,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1486,7 +1299,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1503,7 +1316,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1530,7 +1343,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1547,12 +1360,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1569,12 +1382,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1591,12 +1404,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1613,12 +1426,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1635,12 +1448,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1657,12 +1470,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1679,12 +1492,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1701,12 +1514,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1723,12 +1536,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1745,12 +1558,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1767,12 +1580,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1789,12 +1602,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1811,7 +1624,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1833,12 +1646,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1855,12 +1668,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1877,12 +1690,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1899,12 +1712,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1921,12 +1734,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1943,12 +1756,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1965,12 +1778,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1987,12 +1800,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2009,12 +1822,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2031,12 +1844,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2053,12 +1866,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2075,12 +1888,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2097,12 +1910,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2119,12 +1932,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2141,7 +1954,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2163,7 +1976,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2185,12 +1998,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2207,12 +2020,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2234,7 +2047,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2251,12 +2064,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2273,12 +2086,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2295,12 +2108,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2317,12 +2130,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2339,12 +2152,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2361,12 +2174,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2383,12 +2196,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2405,12 +2218,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2427,12 +2240,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2449,12 +2262,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2471,12 +2284,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2493,12 +2306,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2515,12 +2328,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2537,12 +2350,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2559,12 +2372,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2581,12 +2394,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2603,12 +2416,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2625,12 +2438,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2647,12 +2460,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2669,12 +2482,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2691,12 +2504,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2713,12 +2526,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2735,12 +2548,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2757,12 +2570,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2779,12 +2592,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2801,12 +2614,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2823,12 +2636,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2845,12 +2658,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2867,12 +2680,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2889,12 +2702,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2911,12 +2724,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2933,12 +2746,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2955,12 +2768,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2977,12 +2790,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2999,12 +2812,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3021,12 +2834,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3043,12 +2856,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3057,1106 +2870,6 @@
         </is>
       </c>
       <c r="D84" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -4205,7 +2918,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -4231,7 +2944,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_8.xlsx
+++ b/ttl_long/AdHoc_Net_8.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>84</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>83</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>240</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>189</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>218</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>193</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>123</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>329</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>126</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>222</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>346</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>243</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>310</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>135</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>297</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>393</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>507</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>126</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>416</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>289</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>504</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>554</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>245</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>691</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>599</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>737</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>193</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>661</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>773</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>930</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>233</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>808</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>851</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>969</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>234</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>979</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>327</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1019</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>116</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1168</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1078</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>289</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1118</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1274</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>221</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1312</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>1223</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,131 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1429</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1451</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1575</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1584</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1595</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1123,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1145,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1167,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1189,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1211,7 +1330,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1233,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1255,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1272,12 +1391,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1299,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1316,12 +1435,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1360,12 +1479,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1382,12 +1501,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1404,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1426,12 +1545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1448,12 +1567,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1470,7 +1589,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1492,12 +1611,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1514,12 +1633,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1536,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1558,12 +1677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1580,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1602,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1624,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1646,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1668,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1690,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1712,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1734,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1761,7 +1880,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1783,7 +1902,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1827,7 +1946,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1849,7 +1968,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1871,7 +1990,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1893,7 +2012,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1915,7 +2034,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1932,7 +2051,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1959,7 +2078,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1981,7 +2100,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2003,7 +2122,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2020,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2042,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2069,7 +2188,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2091,7 +2210,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2113,7 +2232,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2135,7 +2254,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2152,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2174,7 +2293,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2196,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2218,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2240,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2262,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2284,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2311,7 +2430,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2333,7 +2452,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2355,7 +2474,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2372,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2416,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2438,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2460,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2482,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2504,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2526,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2548,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2570,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2592,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2614,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2636,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2658,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2680,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2702,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2724,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2746,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2768,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2790,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2812,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2834,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2856,20 +2975,702 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -2918,7 +3719,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -2938,7 +3739,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">

--- a/ttl_long/AdHoc_Net_8.xlsx
+++ b/ttl_long/AdHoc_Net_8.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>104</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>126</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>324</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>179</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>107</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>201</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>291</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>113</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>277</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>152</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>216</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>313</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>280</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>396</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>146</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>321</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>305</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>480</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>163</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>504</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>314</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>509</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>555</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>246</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>646</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>291</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>596</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>788</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>828</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>706</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>956</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>271</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>823</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>344</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>853</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>1002</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>203</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>967</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>980</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1191</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>175</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1154</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>315</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1093</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1183</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1214</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>344</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1204</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>107</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1388</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1442</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>351</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1403</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1548</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>171</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1441</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1529</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1689</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>244</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1690</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D115"/>
+  <dimension ref="A1:D116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1325,12 +1325,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1457,12 +1457,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1677,12 +1677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1699,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1743,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1765,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1787,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1875,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1897,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2029,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2073,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2117,7 +2117,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2161,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2183,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2227,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2249,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2271,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2293,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2337,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2381,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2403,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2447,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2491,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2535,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2579,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2645,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2689,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2711,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2755,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2777,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2843,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2865,7 +2865,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2887,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2909,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2953,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2975,12 +2975,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2997,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3019,7 +3019,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3063,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3107,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3151,12 +3151,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3217,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3239,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3261,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3283,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3305,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3349,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3393,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3415,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3459,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3481,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3503,12 +3503,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3525,7 +3525,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3547,12 +3547,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3569,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3613,12 +3613,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3635,7 +3635,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3657,20 +3657,42 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="C115" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
